--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260819.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260819.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="121">
   <si>
     <t>Symbol</t>
   </si>
@@ -52,27 +52,12 @@
     <t>003690.KS</t>
   </si>
   <si>
-    <t>004170.KS</t>
-  </si>
-  <si>
-    <t>006800.KS</t>
-  </si>
-  <si>
     <t>011780.KS</t>
   </si>
   <si>
-    <t>017800.KS</t>
-  </si>
-  <si>
-    <t>021240.KS</t>
-  </si>
-  <si>
     <t>023530.KS</t>
   </si>
   <si>
-    <t>036570.KS</t>
-  </si>
-  <si>
     <t>039490.KS</t>
   </si>
   <si>
@@ -88,9 +73,6 @@
     <t>271560.KS</t>
   </si>
   <si>
-    <t>443060.KS</t>
-  </si>
-  <si>
     <t>6301.T</t>
   </si>
   <si>
@@ -305,6 +287,9 @@
   </si>
   <si>
     <t>SMH</t>
+  </si>
+  <si>
+    <t>SOXX</t>
   </si>
   <si>
     <t>SPMO</t>
@@ -749,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -786,28 +771,28 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>126900</v>
+        <v>122800</v>
       </c>
       <c r="D2">
-        <v>-3228.77</v>
+        <v>-532.98</v>
       </c>
       <c r="E2">
-        <v>18273600</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H2">
         <v>0.0007</v>
       </c>
       <c r="I2">
-        <v>12791.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -818,25 +803,25 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>1334000</v>
+        <v>1304000</v>
       </c>
       <c r="D3">
-        <v>-44.85</v>
+        <v>-756.21</v>
       </c>
       <c r="E3">
-        <v>46690000</v>
+        <v>45640000</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H3">
         <v>0.0007</v>
       </c>
       <c r="I3">
-        <v>32683</v>
+        <v>31948</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -847,112 +832,112 @@
         <v>4658</v>
       </c>
       <c r="C4">
-        <v>15230</v>
+        <v>14930</v>
       </c>
       <c r="D4">
-        <v>-163.11</v>
+        <v>-1006.41</v>
       </c>
       <c r="E4">
-        <v>70941340</v>
+        <v>69543940</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H4">
         <v>0.0007</v>
       </c>
       <c r="I4">
-        <v>49658.94</v>
+        <v>48680.76</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>12</v>
+      <c r="A5">
+        <v>11200</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>3909</v>
       </c>
       <c r="C5">
-        <v>424500</v>
+        <v>21700</v>
       </c>
       <c r="D5">
-        <v>488.6</v>
+        <v>-2674.5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>84825300</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H5">
         <v>0.0007</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>59377.71</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1434</v>
       </c>
       <c r="C6">
-        <v>36350</v>
+        <v>123600</v>
       </c>
       <c r="D6">
-        <v>-1239.16</v>
+        <v>-2995.02</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>177242400</v>
       </c>
       <c r="F6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H6">
         <v>0.0007</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>124069.68</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7">
-        <v>11200</v>
+      <c r="A7" t="s">
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>3909</v>
+        <v>1182</v>
       </c>
       <c r="C7">
-        <v>22650</v>
+        <v>97100</v>
       </c>
       <c r="D7">
-        <v>4528.25</v>
+        <v>-5022.53</v>
       </c>
       <c r="E7">
-        <v>88538850</v>
+        <v>114772200</v>
       </c>
       <c r="F7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G7" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H7">
         <v>0.0007</v>
       </c>
       <c r="I7">
-        <v>61977.2</v>
+        <v>80340.53999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -960,927 +945,927 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>1434</v>
+        <v>84</v>
       </c>
       <c r="C8">
-        <v>126500</v>
+        <v>265500</v>
       </c>
       <c r="D8">
-        <v>-3269.71</v>
+        <v>-1088.94</v>
       </c>
       <c r="E8">
-        <v>181401000</v>
+        <v>22302000</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H8">
         <v>0.0007</v>
       </c>
       <c r="I8">
-        <v>126980.7</v>
+        <v>15611.4</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>15</v>
+      <c r="A9">
+        <v>51900</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>74300</v>
+        <v>302000</v>
       </c>
       <c r="D9">
-        <v>1353.7</v>
+        <v>20.17</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>4228000</v>
       </c>
       <c r="F9" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H9">
         <v>0.0007</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2959.6</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="C10">
-        <v>96500</v>
+        <v>94800</v>
       </c>
       <c r="D10">
-        <v>-436.79</v>
+        <v>-3123.36</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>79063200</v>
       </c>
       <c r="F10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H10">
         <v>0.0007</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>55344.24</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>17</v>
+      <c r="A11">
+        <v>71050</v>
       </c>
       <c r="B11">
-        <v>1182</v>
+        <v>391</v>
       </c>
       <c r="C11">
-        <v>103000</v>
+        <v>183100</v>
       </c>
       <c r="D11">
-        <v>134.59</v>
+        <v>-2393.58</v>
       </c>
       <c r="E11">
-        <v>121746000</v>
+        <v>71592100</v>
       </c>
       <c r="F11" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H11">
         <v>0.0007</v>
       </c>
       <c r="I11">
-        <v>85222.2</v>
+        <v>50114.47</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>34898</v>
       </c>
       <c r="C12">
-        <v>230000</v>
+        <v>5340</v>
       </c>
       <c r="D12">
-        <v>-1269.56</v>
+        <v>-4524.04</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>186355320</v>
       </c>
       <c r="F12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H12">
         <v>0.0007</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>130448.72</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>19</v>
+      <c r="A13">
+        <v>1109</v>
       </c>
       <c r="B13">
-        <v>84</v>
+        <v>2000</v>
       </c>
       <c r="C13">
-        <v>283500</v>
+        <v>34.16</v>
       </c>
       <c r="D13">
-        <v>-1737.55</v>
+        <v>-20.4</v>
       </c>
       <c r="E13">
-        <v>23814000</v>
+        <v>68320</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H13">
-        <v>0.0007</v>
+        <v>0.1275</v>
       </c>
       <c r="I13">
-        <v>16669.8</v>
+        <v>8710.799999999999</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>51900</v>
+        <v>1258</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="C14">
-        <v>300000</v>
+        <v>14.35</v>
       </c>
       <c r="D14">
-        <v>7.5</v>
+        <v>-39.53</v>
       </c>
       <c r="E14">
-        <v>4200000</v>
+        <v>14350</v>
       </c>
       <c r="F14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H14">
-        <v>0.0007</v>
+        <v>0.1275</v>
       </c>
       <c r="I14">
-        <v>2940</v>
+        <v>1829.62</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>20</v>
+      <c r="A15">
+        <v>1288</v>
       </c>
       <c r="B15">
-        <v>834</v>
+        <v>6000</v>
       </c>
       <c r="C15">
-        <v>100000</v>
+        <v>6.22</v>
       </c>
       <c r="D15">
-        <v>-2391.65</v>
+        <v>99.47</v>
       </c>
       <c r="E15">
-        <v>83400000</v>
+        <v>37320</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H15">
-        <v>0.0007</v>
+        <v>0.1275</v>
       </c>
       <c r="I15">
-        <v>58380</v>
+        <v>4758.3</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>71050</v>
+        <v>1398</v>
       </c>
       <c r="B16">
-        <v>391</v>
+        <v>1566000</v>
       </c>
       <c r="C16">
-        <v>191600</v>
+        <v>7.385</v>
       </c>
       <c r="D16">
-        <v>-2490.46</v>
+        <v>21968.32</v>
       </c>
       <c r="E16">
-        <v>74915600</v>
+        <v>11564910</v>
       </c>
       <c r="F16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H16">
+        <v>0.1275</v>
+      </c>
+      <c r="I16">
+        <v>1474526.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>1698</v>
+      </c>
+      <c r="B17">
+        <v>2000</v>
+      </c>
+      <c r="C17">
+        <v>34.24</v>
+      </c>
+      <c r="D17">
+        <v>-91.81999999999999</v>
+      </c>
+      <c r="E17">
+        <v>68480</v>
+      </c>
+      <c r="F17" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17">
+        <v>0.1275</v>
+      </c>
+      <c r="I17">
+        <v>8731.200000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>109</v>
+      </c>
+      <c r="C18">
+        <v>116300</v>
+      </c>
+      <c r="D18">
+        <v>-204.1</v>
+      </c>
+      <c r="E18">
+        <v>12676700</v>
+      </c>
+      <c r="F18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18">
         <v>0.0007</v>
       </c>
-      <c r="I16">
-        <v>52440.92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17">
-        <v>34898</v>
-      </c>
-      <c r="C17">
-        <v>5520</v>
-      </c>
-      <c r="D17">
-        <v>-2670.77</v>
-      </c>
-      <c r="E17">
-        <v>192636960</v>
-      </c>
-      <c r="F17" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17">
-        <v>0.0007</v>
-      </c>
-      <c r="I17">
-        <v>134845.87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
-        <v>1109</v>
-      </c>
-      <c r="B18">
-        <v>2000</v>
-      </c>
-      <c r="C18">
-        <v>34.24</v>
-      </c>
-      <c r="D18">
-        <v>71.39</v>
-      </c>
-      <c r="E18">
-        <v>68480</v>
-      </c>
-      <c r="F18" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18">
-        <v>0.1275</v>
-      </c>
       <c r="I18">
-        <v>8731.200000000001</v>
+        <v>8873.690000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>1258</v>
+        <v>1810</v>
       </c>
       <c r="B19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="C19">
-        <v>14.66</v>
+        <v>27.44</v>
       </c>
       <c r="D19">
-        <v>-43.34</v>
+        <v>32.14</v>
       </c>
       <c r="E19">
-        <v>14660</v>
+        <v>5488</v>
       </c>
       <c r="F19" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H19">
         <v>0.1275</v>
       </c>
       <c r="I19">
-        <v>1869.15</v>
+        <v>699.72</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>1288</v>
+        <v>2359</v>
       </c>
       <c r="B20">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="C20">
-        <v>6.09</v>
+        <v>202</v>
       </c>
       <c r="D20">
-        <v>145.33</v>
+        <v>-122.43</v>
       </c>
       <c r="E20">
-        <v>36540</v>
+        <v>60600</v>
       </c>
       <c r="F20" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H20">
         <v>0.1275</v>
       </c>
       <c r="I20">
-        <v>4658.85</v>
+        <v>7726.5</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21">
-        <v>1398</v>
+      <c r="A21" t="s">
+        <v>18</v>
       </c>
       <c r="B21">
-        <v>1566000</v>
+        <v>104</v>
       </c>
       <c r="C21">
-        <v>7.275</v>
+        <v>124100</v>
       </c>
       <c r="D21">
-        <v>10979.85</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="E21">
-        <v>11392650</v>
+        <v>12906400</v>
       </c>
       <c r="F21" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H21">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I21">
-        <v>1452562.88</v>
+        <v>9034.48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>1698</v>
+        <v>2800</v>
       </c>
       <c r="B22">
         <v>2000</v>
       </c>
       <c r="C22">
-        <v>34.6</v>
+        <v>26</v>
       </c>
       <c r="D22">
-        <v>50.99</v>
+        <v>10.2</v>
       </c>
       <c r="E22">
-        <v>69200</v>
+        <v>52000</v>
       </c>
       <c r="F22" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G22" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H22">
         <v>0.1275</v>
       </c>
       <c r="I22">
-        <v>8823</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>22</v>
+      <c r="A23">
+        <v>2828</v>
       </c>
       <c r="B23">
-        <v>109</v>
+        <v>600</v>
       </c>
       <c r="C23">
-        <v>118900</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D23">
-        <v>-736.3200000000001</v>
+        <v>15.3</v>
       </c>
       <c r="E23">
-        <v>12960100</v>
+        <v>52260</v>
       </c>
       <c r="F23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H23">
-        <v>0.0007</v>
+        <v>0.1275</v>
       </c>
       <c r="I23">
-        <v>9072.07</v>
+        <v>6663.15</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>1810</v>
+        <v>2899</v>
       </c>
       <c r="B24">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="C24">
-        <v>26.18</v>
+        <v>34.9</v>
       </c>
       <c r="D24">
-        <v>7.65</v>
+        <v>-153.04</v>
       </c>
       <c r="E24">
-        <v>5236</v>
+        <v>69800</v>
       </c>
       <c r="F24" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H24">
         <v>0.1275</v>
       </c>
       <c r="I24">
-        <v>667.59</v>
+        <v>8899.5</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>2359</v>
+        <v>3067</v>
       </c>
       <c r="B25">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="C25">
-        <v>205.2</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="D25">
-        <v>68.84</v>
+        <v>-10.71</v>
       </c>
       <c r="E25">
-        <v>61560</v>
+        <v>6923</v>
       </c>
       <c r="F25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H25">
         <v>0.1275</v>
       </c>
       <c r="I25">
-        <v>7848.9</v>
+        <v>882.6799999999999</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>23</v>
+      <c r="A26">
+        <v>3750</v>
       </c>
       <c r="B26">
-        <v>104</v>
+        <v>4700</v>
       </c>
       <c r="C26">
-        <v>125100</v>
+        <v>628.5</v>
       </c>
       <c r="D26">
-        <v>-608.48</v>
+        <v>-13186.6</v>
       </c>
       <c r="E26">
-        <v>13010400</v>
+        <v>2953950</v>
       </c>
       <c r="F26" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H26">
-        <v>0.0007</v>
+        <v>0.1275</v>
       </c>
       <c r="I26">
-        <v>9107.280000000001</v>
+        <v>376628.62</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
-        <v>2800</v>
+        <v>388</v>
       </c>
       <c r="B27">
-        <v>2000</v>
+        <v>33000</v>
       </c>
       <c r="C27">
-        <v>25.96</v>
+        <v>414.6</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>40401.5</v>
       </c>
       <c r="E27">
-        <v>51920</v>
+        <v>13681800</v>
       </c>
       <c r="F27" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H27">
         <v>0.1275</v>
       </c>
       <c r="I27">
-        <v>6619.8</v>
+        <v>1744429.5</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28">
-        <v>2828</v>
+        <v>3988</v>
       </c>
       <c r="B28">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="C28">
-        <v>86.90000000000001</v>
+        <v>5.41</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>107.88</v>
       </c>
       <c r="E28">
-        <v>52140</v>
+        <v>21640</v>
       </c>
       <c r="F28" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H28">
         <v>0.1275</v>
       </c>
       <c r="I28">
-        <v>6647.85</v>
+        <v>2759.1</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29">
-        <v>2899</v>
+      <c r="A29" t="s">
+        <v>19</v>
       </c>
       <c r="B29">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="C29">
-        <v>35.5</v>
+        <v>6807</v>
       </c>
       <c r="D29">
-        <v>-107.08</v>
+        <v>-41085.55</v>
       </c>
       <c r="E29">
-        <v>71000</v>
+        <v>122526000</v>
       </c>
       <c r="F29" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H29">
-        <v>0.1275</v>
+        <v>0.0063</v>
       </c>
       <c r="I29">
-        <v>9052.5</v>
+        <v>771913.8</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30">
-        <v>3067</v>
+      <c r="A30" t="s">
+        <v>20</v>
       </c>
       <c r="B30">
-        <v>700</v>
+        <v>12000</v>
       </c>
       <c r="C30">
-        <v>10.01</v>
+        <v>7331</v>
       </c>
       <c r="D30">
-        <v>-8.029999999999999</v>
+        <v>-12519.14</v>
       </c>
       <c r="E30">
-        <v>7007</v>
+        <v>87972000</v>
       </c>
       <c r="F30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H30">
-        <v>0.1275</v>
+        <v>0.0063</v>
       </c>
       <c r="I30">
-        <v>893.39</v>
+        <v>554223.6</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31">
-        <v>3750</v>
+        <v>700</v>
       </c>
       <c r="B31">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="C31">
-        <v>650.5</v>
+        <v>447.2</v>
       </c>
       <c r="D31">
-        <v>-898.73</v>
+        <v>61.21</v>
       </c>
       <c r="E31">
-        <v>3057350</v>
+        <v>44720</v>
       </c>
       <c r="F31" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H31">
         <v>0.1275</v>
       </c>
       <c r="I31">
-        <v>389812.12</v>
+        <v>5701.8</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32">
-        <v>388</v>
+      <c r="A32" t="s">
+        <v>21</v>
       </c>
       <c r="B32">
-        <v>33000</v>
+        <v>2600</v>
       </c>
       <c r="C32">
-        <v>405</v>
+        <v>7100</v>
       </c>
       <c r="D32">
-        <v>-5048.21</v>
+        <v>-7233.28</v>
       </c>
       <c r="E32">
-        <v>13365000</v>
+        <v>18460000</v>
       </c>
       <c r="F32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H32">
-        <v>0.1275</v>
+        <v>0.0063</v>
       </c>
       <c r="I32">
-        <v>1704037.5</v>
+        <v>116298</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33">
-        <v>3988</v>
+        <v>9633</v>
       </c>
       <c r="B33">
-        <v>4000</v>
+        <v>1800</v>
       </c>
       <c r="C33">
-        <v>5.32</v>
+        <v>42.14</v>
       </c>
       <c r="D33">
-        <v>7.65</v>
+        <v>238.52</v>
       </c>
       <c r="E33">
-        <v>21280</v>
+        <v>75852</v>
       </c>
       <c r="F33" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H33">
         <v>0.1275</v>
       </c>
       <c r="I33">
-        <v>2713.2</v>
+        <v>9671.129999999999</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>55700</v>
       </c>
       <c r="C34">
-        <v>204000</v>
+        <v>2.63</v>
       </c>
       <c r="D34">
-        <v>287.86</v>
+        <v>-1752.77</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>146491</v>
       </c>
       <c r="F34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H34">
-        <v>0.0007</v>
+        <v>0.7867</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>115244.47</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B35">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="C35">
-        <v>7168</v>
+        <v>2.42</v>
       </c>
       <c r="D35">
-        <v>-4848.88</v>
+        <v>-47.2</v>
       </c>
       <c r="E35">
-        <v>129024000</v>
+        <v>14520</v>
       </c>
       <c r="F35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H35">
-        <v>0.0063</v>
+        <v>0.7867</v>
       </c>
       <c r="I35">
-        <v>812851.2</v>
+        <v>11422.88</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B36">
-        <v>12000</v>
+        <v>13900</v>
       </c>
       <c r="C36">
-        <v>7496</v>
+        <v>110.71</v>
       </c>
       <c r="D36">
-        <v>-59690.06</v>
+        <v>13622</v>
       </c>
       <c r="E36">
-        <v>89952000</v>
+        <v>1538869</v>
       </c>
       <c r="F36" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H36">
-        <v>0.0063</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>566697.6</v>
+        <v>1538869</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37">
-        <v>700</v>
+      <c r="A37" t="s">
+        <v>25</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>10375</v>
       </c>
       <c r="C37">
-        <v>442.4</v>
+        <v>93.05</v>
       </c>
       <c r="D37">
-        <v>-50.99</v>
+        <v>10478.75</v>
       </c>
       <c r="E37">
-        <v>44240</v>
+        <v>965393.75</v>
       </c>
       <c r="F37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H37">
-        <v>0.1275</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>5640.6</v>
+        <v>965393.75</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38">
+        <v>10</v>
+      </c>
+      <c r="C38">
+        <v>126.47</v>
+      </c>
+      <c r="D38">
+        <v>-2.4</v>
+      </c>
+      <c r="E38">
+        <v>1264.7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" t="s">
+        <v>118</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>1264.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
         <v>27</v>
       </c>
-      <c r="B38">
-        <v>2600</v>
-      </c>
-      <c r="C38">
-        <v>7540</v>
-      </c>
-      <c r="D38">
-        <v>-814.41</v>
-      </c>
-      <c r="E38">
-        <v>19604000</v>
-      </c>
-      <c r="F38" t="s">
-        <v>120</v>
-      </c>
-      <c r="G38" t="s">
-        <v>123</v>
-      </c>
-      <c r="H38">
-        <v>0.0063</v>
-      </c>
-      <c r="I38">
-        <v>123505.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39">
-        <v>9633</v>
-      </c>
       <c r="B39">
-        <v>1800</v>
+        <v>7000</v>
       </c>
       <c r="C39">
-        <v>42.16</v>
+        <v>128.9</v>
       </c>
       <c r="D39">
-        <v>-82.61</v>
+        <v>5250</v>
       </c>
       <c r="E39">
-        <v>75888</v>
+        <v>902300</v>
       </c>
       <c r="F39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G39" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H39">
-        <v>0.1275</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>9675.719999999999</v>
+        <v>902300</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1888,28 +1873,28 @@
         <v>28</v>
       </c>
       <c r="B40">
-        <v>55700</v>
+        <v>31000</v>
       </c>
       <c r="C40">
-        <v>2.67</v>
+        <v>63.17</v>
       </c>
       <c r="D40">
-        <v>-3049.76</v>
+        <v>-32860</v>
       </c>
       <c r="E40">
-        <v>148719</v>
+        <v>1958270</v>
       </c>
       <c r="F40" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G40" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H40">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>116328</v>
+        <v>1958270</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1917,28 +1902,28 @@
         <v>29</v>
       </c>
       <c r="B41">
-        <v>6000</v>
+        <v>70</v>
       </c>
       <c r="C41">
-        <v>2.43</v>
+        <v>20.24</v>
       </c>
       <c r="D41">
-        <v>-46.93</v>
+        <v>137.2</v>
       </c>
       <c r="E41">
-        <v>14580</v>
+        <v>1416.8</v>
       </c>
       <c r="F41" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G41" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H41">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>11404.48</v>
+        <v>1416.8</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1946,28 +1931,28 @@
         <v>30</v>
       </c>
       <c r="B42">
-        <v>13900</v>
+        <v>3000</v>
       </c>
       <c r="C42">
-        <v>109.73</v>
+        <v>11.23</v>
       </c>
       <c r="D42">
-        <v>-20433</v>
+        <v>-212.41</v>
       </c>
       <c r="E42">
-        <v>1525247</v>
+        <v>33690</v>
       </c>
       <c r="F42" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G42" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I42">
-        <v>1525247</v>
+        <v>26503.92</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1975,28 +1960,28 @@
         <v>31</v>
       </c>
       <c r="B43">
-        <v>10375</v>
+        <v>821</v>
       </c>
       <c r="C43">
-        <v>92.04000000000001</v>
+        <v>162.26</v>
       </c>
       <c r="D43">
-        <v>-25626.25</v>
+        <v>-2257.75</v>
       </c>
       <c r="E43">
-        <v>954915</v>
+        <v>133215.46</v>
       </c>
       <c r="F43" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G43" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>954915</v>
+        <v>133215.46</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2004,28 +1989,28 @@
         <v>32</v>
       </c>
       <c r="B44">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C44">
-        <v>126.71</v>
+        <v>6.97</v>
       </c>
       <c r="D44">
-        <v>-15.2</v>
+        <v>-6.29</v>
       </c>
       <c r="E44">
-        <v>1267.1</v>
+        <v>1394</v>
       </c>
       <c r="F44" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G44" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I44">
-        <v>1267.1</v>
+        <v>1096.66</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2033,28 +2018,28 @@
         <v>33</v>
       </c>
       <c r="B45">
-        <v>7000</v>
+        <v>15</v>
       </c>
       <c r="C45">
-        <v>128.15</v>
+        <v>274.17</v>
       </c>
       <c r="D45">
-        <v>24080</v>
+        <v>110.1</v>
       </c>
       <c r="E45">
-        <v>897050</v>
+        <v>4112.55</v>
       </c>
       <c r="F45" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G45" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>897050</v>
+        <v>4112.55</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2062,28 +2047,28 @@
         <v>34</v>
       </c>
       <c r="B46">
-        <v>31000</v>
+        <v>888013</v>
       </c>
       <c r="C46">
-        <v>64.23</v>
+        <v>33.29</v>
       </c>
       <c r="D46">
-        <v>10540</v>
+        <v>-439040.93</v>
       </c>
       <c r="E46">
-        <v>1991130</v>
+        <v>29561952.77</v>
       </c>
       <c r="F46" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G46" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>1991130</v>
+        <v>29561952.77</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2091,28 +2076,28 @@
         <v>35</v>
       </c>
       <c r="B47">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>18.28</v>
+        <v>266.94</v>
       </c>
       <c r="D47">
-        <v>-31.5</v>
+        <v>-133.4</v>
       </c>
       <c r="E47">
-        <v>1279.6</v>
+        <v>7741.26</v>
       </c>
       <c r="F47" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G47" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>1279.6</v>
+        <v>7741.26</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2120,28 +2105,28 @@
         <v>36</v>
       </c>
       <c r="B48">
-        <v>3000</v>
+        <v>98183</v>
       </c>
       <c r="C48">
-        <v>11.32</v>
+        <v>49.88</v>
       </c>
       <c r="D48">
-        <v>-445.85</v>
+        <v>-240548.35</v>
       </c>
       <c r="E48">
-        <v>33960</v>
+        <v>4897368.04</v>
       </c>
       <c r="F48" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G48" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H48">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>26563.51</v>
+        <v>4897368.04</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2149,28 +2134,28 @@
         <v>37</v>
       </c>
       <c r="B49">
-        <v>821</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>165.01</v>
+        <v>160.2</v>
       </c>
       <c r="D49">
-        <v>-5361.13</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="E49">
-        <v>135473.21</v>
+        <v>801</v>
       </c>
       <c r="F49" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G49" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49">
-        <v>135473.21</v>
+        <v>801</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2178,28 +2163,28 @@
         <v>38</v>
       </c>
       <c r="B50">
-        <v>200</v>
+        <v>2470</v>
       </c>
       <c r="C50">
-        <v>7.01</v>
+        <v>49.81</v>
       </c>
       <c r="D50">
-        <v>-14.08</v>
+        <v>2692.3</v>
       </c>
       <c r="E50">
-        <v>1402</v>
+        <v>123030.7</v>
       </c>
       <c r="F50" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G50" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H50">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>1096.64</v>
+        <v>123030.7</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2207,28 +2192,28 @@
         <v>39</v>
       </c>
       <c r="B51">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51">
-        <v>266.83</v>
+        <v>110.55</v>
       </c>
       <c r="D51">
-        <v>-170.55</v>
+        <v>-13.78</v>
       </c>
       <c r="E51">
-        <v>4002.45</v>
+        <v>1437.15</v>
       </c>
       <c r="F51" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G51" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>4002.45</v>
+        <v>1437.15</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2236,28 +2221,28 @@
         <v>40</v>
       </c>
       <c r="B52">
-        <v>857613</v>
+        <v>10</v>
       </c>
       <c r="C52">
-        <v>33.8</v>
+        <v>203.08</v>
       </c>
       <c r="D52">
-        <v>-85761.3</v>
+        <v>36.3</v>
       </c>
       <c r="E52">
-        <v>28987319.4</v>
+        <v>2030.8</v>
       </c>
       <c r="F52" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G52" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>28987319.4</v>
+        <v>2030.8</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2265,28 +2250,28 @@
         <v>41</v>
       </c>
       <c r="B53">
-        <v>29</v>
+        <v>800</v>
       </c>
       <c r="C53">
-        <v>271.54</v>
+        <v>76</v>
       </c>
       <c r="D53">
-        <v>106.14</v>
+        <v>176.22</v>
       </c>
       <c r="E53">
-        <v>7874.66</v>
+        <v>60800</v>
       </c>
       <c r="F53" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G53" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I53">
-        <v>7874.66</v>
+        <v>47831.36</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2294,28 +2279,28 @@
         <v>42</v>
       </c>
       <c r="B54">
-        <v>98183</v>
+        <v>516023</v>
       </c>
       <c r="C54">
-        <v>52.33</v>
+        <v>30.94</v>
       </c>
       <c r="D54">
-        <v>-131565.22</v>
+        <v>-170287.59</v>
       </c>
       <c r="E54">
-        <v>5137916.39</v>
+        <v>15965751.62</v>
       </c>
       <c r="F54" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H54">
         <v>1</v>
       </c>
       <c r="I54">
-        <v>5137916.39</v>
+        <v>15965751.62</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2323,28 +2308,28 @@
         <v>43</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>-4000</v>
       </c>
       <c r="C55">
-        <v>146.23</v>
+        <v>233.52</v>
       </c>
       <c r="D55">
-        <v>-21.6</v>
+        <v>30426.69</v>
       </c>
       <c r="E55">
-        <v>731.15</v>
+        <v>-934080</v>
       </c>
       <c r="F55" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G55" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="I55">
-        <v>731.15</v>
+        <v>-934080</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2352,28 +2337,28 @@
         <v>44</v>
       </c>
       <c r="B56">
-        <v>2470</v>
+        <v>5000</v>
       </c>
       <c r="C56">
-        <v>48.72</v>
+        <v>122.31</v>
       </c>
       <c r="D56">
-        <v>-24.7</v>
+        <v>7350</v>
       </c>
       <c r="E56">
-        <v>120338.4</v>
+        <v>611550</v>
       </c>
       <c r="F56" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G56" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56">
-        <v>120338.4</v>
+        <v>611550</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2381,28 +2366,28 @@
         <v>45</v>
       </c>
       <c r="B57">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>111.61</v>
+        <v>107.66</v>
       </c>
       <c r="D57">
-        <v>-16.77</v>
+        <v>0.39</v>
       </c>
       <c r="E57">
-        <v>1450.93</v>
+        <v>107.66</v>
       </c>
       <c r="F57" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G57" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57">
-        <v>1450.93</v>
+        <v>107.66</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2410,28 +2395,28 @@
         <v>46</v>
       </c>
       <c r="B58">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C58">
-        <v>199.45</v>
+        <v>157.6</v>
       </c>
       <c r="D58">
-        <v>16.3</v>
+        <v>-6.48</v>
       </c>
       <c r="E58">
-        <v>1994.5</v>
+        <v>5673.6</v>
       </c>
       <c r="F58" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G58" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58">
-        <v>1994.5</v>
+        <v>5673.6</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2439,28 +2424,28 @@
         <v>47</v>
       </c>
       <c r="B59">
-        <v>800</v>
+        <v>3332</v>
       </c>
       <c r="C59">
-        <v>75.72</v>
+        <v>36.44</v>
       </c>
       <c r="D59">
-        <v>-725.87</v>
+        <v>1499.4</v>
       </c>
       <c r="E59">
-        <v>60576</v>
+        <v>121418.08</v>
       </c>
       <c r="F59" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G59" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H59">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>47382.55</v>
+        <v>121418.08</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2468,28 +2453,28 @@
         <v>48</v>
       </c>
       <c r="B60">
-        <v>516023</v>
+        <v>2727</v>
       </c>
       <c r="C60">
-        <v>31.27</v>
+        <v>44.6</v>
       </c>
       <c r="D60">
-        <v>-139326.21</v>
+        <v>2645.19</v>
       </c>
       <c r="E60">
-        <v>16136039.21</v>
+        <v>121624.2</v>
       </c>
       <c r="F60" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G60" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H60">
         <v>1</v>
       </c>
       <c r="I60">
-        <v>16136039.21</v>
+        <v>121624.2</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2497,28 +2482,28 @@
         <v>49</v>
       </c>
       <c r="B61">
-        <v>-2000</v>
+        <v>17</v>
       </c>
       <c r="C61">
-        <v>246</v>
+        <v>424.67</v>
       </c>
       <c r="D61">
-        <v>2640</v>
+        <v>-113.22</v>
       </c>
       <c r="E61">
-        <v>-492000</v>
+        <v>7219.39</v>
       </c>
       <c r="F61" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>-492000</v>
+        <v>7219.39</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2526,28 +2511,28 @@
         <v>50</v>
       </c>
       <c r="B62">
-        <v>5000</v>
+        <v>1928</v>
       </c>
       <c r="C62">
-        <v>120.84</v>
+        <v>61.83</v>
       </c>
       <c r="D62">
-        <v>3800</v>
+        <v>482</v>
       </c>
       <c r="E62">
-        <v>604200</v>
+        <v>119208.24</v>
       </c>
       <c r="F62" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G62" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>604200</v>
+        <v>119208.24</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2555,28 +2540,28 @@
         <v>51</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2268</v>
       </c>
       <c r="C63">
-        <v>107.27</v>
+        <v>52.91</v>
       </c>
       <c r="D63">
-        <v>-1.18</v>
+        <v>1247.4</v>
       </c>
       <c r="E63">
-        <v>107.27</v>
+        <v>119999.88</v>
       </c>
       <c r="F63" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G63" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>107.27</v>
+        <v>119999.88</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2584,28 +2569,28 @@
         <v>52</v>
       </c>
       <c r="B64">
-        <v>36</v>
+        <v>2717</v>
       </c>
       <c r="C64">
-        <v>157.78</v>
+        <v>44.04</v>
       </c>
       <c r="D64">
-        <v>-153.72</v>
+        <v>978.12</v>
       </c>
       <c r="E64">
-        <v>5680.08</v>
+        <v>119656.68</v>
       </c>
       <c r="F64" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G64" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>5680.08</v>
+        <v>119656.68</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2613,28 +2598,28 @@
         <v>53</v>
       </c>
       <c r="B65">
-        <v>3332</v>
+        <v>1896</v>
       </c>
       <c r="C65">
-        <v>35.99</v>
+        <v>62.83</v>
       </c>
       <c r="D65">
-        <v>-866.3200000000001</v>
+        <v>208.56</v>
       </c>
       <c r="E65">
-        <v>119918.68</v>
+        <v>119125.68</v>
       </c>
       <c r="F65" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G65" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>119918.68</v>
+        <v>119125.68</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2642,28 +2627,28 @@
         <v>54</v>
       </c>
       <c r="B66">
-        <v>2727</v>
+        <v>1909</v>
       </c>
       <c r="C66">
-        <v>43.63</v>
+        <v>62.36</v>
       </c>
       <c r="D66">
-        <v>-899.91</v>
+        <v>534.52</v>
       </c>
       <c r="E66">
-        <v>118979.01</v>
+        <v>119045.24</v>
       </c>
       <c r="F66" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G66" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>118979.01</v>
+        <v>119045.24</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2671,28 +2656,28 @@
         <v>55</v>
       </c>
       <c r="B67">
-        <v>17</v>
+        <v>2528</v>
       </c>
       <c r="C67">
-        <v>431.33</v>
+        <v>47.16</v>
       </c>
       <c r="D67">
-        <v>-409.19</v>
+        <v>1036.48</v>
       </c>
       <c r="E67">
-        <v>7332.61</v>
+        <v>119220.48</v>
       </c>
       <c r="F67" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G67" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67">
-        <v>7332.61</v>
+        <v>119220.48</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2700,28 +2685,28 @@
         <v>56</v>
       </c>
       <c r="B68">
-        <v>1928</v>
+        <v>3502</v>
       </c>
       <c r="C68">
-        <v>61.58</v>
+        <v>33.72</v>
       </c>
       <c r="D68">
-        <v>-1156.8</v>
+        <v>875.5</v>
       </c>
       <c r="E68">
-        <v>118726.24</v>
+        <v>118087.44</v>
       </c>
       <c r="F68" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G68" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68">
-        <v>118726.24</v>
+        <v>118087.44</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2729,28 +2714,28 @@
         <v>57</v>
       </c>
       <c r="B69">
-        <v>2268</v>
+        <v>27000</v>
       </c>
       <c r="C69">
-        <v>52.36</v>
+        <v>174.43</v>
       </c>
       <c r="D69">
-        <v>-249.48</v>
+        <v>118260</v>
       </c>
       <c r="E69">
-        <v>118752.48</v>
+        <v>4709610</v>
       </c>
       <c r="F69" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G69" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H69">
         <v>1</v>
       </c>
       <c r="I69">
-        <v>118752.48</v>
+        <v>4709610</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2758,28 +2743,28 @@
         <v>58</v>
       </c>
       <c r="B70">
-        <v>2717</v>
+        <v>47320</v>
       </c>
       <c r="C70">
-        <v>43.68</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D70">
-        <v>-760.76</v>
+        <v>9841.040000000001</v>
       </c>
       <c r="E70">
-        <v>118678.56</v>
+        <v>3388112</v>
       </c>
       <c r="F70" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G70" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>118678.56</v>
+        <v>3388112</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2787,28 +2772,28 @@
         <v>59</v>
       </c>
       <c r="B71">
-        <v>1896</v>
+        <v>62</v>
       </c>
       <c r="C71">
-        <v>62.72</v>
+        <v>987.46</v>
       </c>
       <c r="D71">
-        <v>-682.5599999999999</v>
+        <v>-1058.34</v>
       </c>
       <c r="E71">
-        <v>118917.12</v>
+        <v>61222.52</v>
       </c>
       <c r="F71" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G71" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>118917.12</v>
+        <v>61222.52</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2816,28 +2801,28 @@
         <v>60</v>
       </c>
       <c r="B72">
-        <v>1909</v>
+        <v>6400</v>
       </c>
       <c r="C72">
-        <v>62.08</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="D72">
-        <v>-610.88</v>
+        <v>21184</v>
       </c>
       <c r="E72">
-        <v>118510.72</v>
+        <v>571456</v>
       </c>
       <c r="F72" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G72" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72">
-        <v>118510.72</v>
+        <v>571456</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2845,28 +2830,28 @@
         <v>61</v>
       </c>
       <c r="B73">
-        <v>2528</v>
+        <v>2160</v>
       </c>
       <c r="C73">
-        <v>46.75</v>
+        <v>344.72</v>
       </c>
       <c r="D73">
-        <v>-985.92</v>
+        <v>1123.2</v>
       </c>
       <c r="E73">
-        <v>118184</v>
+        <v>744595.2</v>
       </c>
       <c r="F73" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G73" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73">
-        <v>118184</v>
+        <v>744595.2</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2874,28 +2859,28 @@
         <v>62</v>
       </c>
       <c r="B74">
-        <v>3502</v>
+        <v>1448</v>
       </c>
       <c r="C74">
-        <v>33.47</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="D74">
-        <v>-1575.9</v>
+        <v>637.12</v>
       </c>
       <c r="E74">
-        <v>117211.94</v>
+        <v>120401.2</v>
       </c>
       <c r="F74" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G74" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>117211.94</v>
+        <v>120401.2</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2903,28 +2888,28 @@
         <v>63</v>
       </c>
       <c r="B75">
-        <v>27000</v>
+        <v>118000</v>
       </c>
       <c r="C75">
-        <v>170.05</v>
+        <v>34.66</v>
       </c>
       <c r="D75">
-        <v>-406350</v>
+        <v>50740</v>
       </c>
       <c r="E75">
-        <v>4591350</v>
+        <v>4089880</v>
       </c>
       <c r="F75" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G75" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>4591350</v>
+        <v>4089880</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2932,28 +2917,28 @@
         <v>64</v>
       </c>
       <c r="B76">
-        <v>35000</v>
+        <v>42</v>
       </c>
       <c r="C76">
-        <v>71.34</v>
+        <v>157.24</v>
       </c>
       <c r="D76">
-        <v>-19950</v>
+        <v>44.52</v>
       </c>
       <c r="E76">
-        <v>2496900</v>
+        <v>6604.08</v>
       </c>
       <c r="F76" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G76" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <v>2496900</v>
+        <v>6604.08</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2961,28 +2946,28 @@
         <v>65</v>
       </c>
       <c r="B77">
-        <v>62</v>
+        <v>1926</v>
       </c>
       <c r="C77">
-        <v>1004.53</v>
+        <v>62.306</v>
       </c>
       <c r="D77">
-        <v>-4617.14</v>
+        <v>891.16</v>
       </c>
       <c r="E77">
-        <v>62280.86</v>
+        <v>120001.36</v>
       </c>
       <c r="F77" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G77" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>62280.86</v>
+        <v>120001.36</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2990,28 +2975,28 @@
         <v>66</v>
       </c>
       <c r="B78">
-        <v>6400</v>
+        <v>430000</v>
       </c>
       <c r="C78">
-        <v>85.98</v>
+        <v>24.23</v>
       </c>
       <c r="D78">
-        <v>-9408</v>
+        <v>-21500</v>
       </c>
       <c r="E78">
-        <v>550272</v>
+        <v>10418900</v>
       </c>
       <c r="F78" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G78" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <v>550272</v>
+        <v>10418900</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3019,28 +3004,28 @@
         <v>67</v>
       </c>
       <c r="B79">
-        <v>2160</v>
+        <v>8500</v>
       </c>
       <c r="C79">
-        <v>344.2</v>
+        <v>357.26</v>
       </c>
       <c r="D79">
-        <v>432</v>
+        <v>-50915</v>
       </c>
       <c r="E79">
-        <v>743472</v>
+        <v>3036710</v>
       </c>
       <c r="F79" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G79" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H79">
         <v>1</v>
       </c>
       <c r="I79">
-        <v>743472</v>
+        <v>3036710</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3048,28 +3033,28 @@
         <v>68</v>
       </c>
       <c r="B80">
-        <v>1448</v>
+        <v>333</v>
       </c>
       <c r="C80">
-        <v>82.70999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="D80">
-        <v>-605.99</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>119764.08</v>
+        <v>291.38</v>
       </c>
       <c r="F80" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G80" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I80">
-        <v>119764.08</v>
+        <v>229.23</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3077,28 +3062,28 @@
         <v>69</v>
       </c>
       <c r="B81">
-        <v>118000</v>
+        <v>874744</v>
       </c>
       <c r="C81">
-        <v>34.23</v>
+        <v>29.01</v>
       </c>
       <c r="D81">
-        <v>-12980</v>
+        <v>-306160.4</v>
       </c>
       <c r="E81">
-        <v>4039140</v>
+        <v>25376323.44</v>
       </c>
       <c r="F81" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G81" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
       <c r="I81">
-        <v>4039140</v>
+        <v>25376323.44</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3106,28 +3091,28 @@
         <v>70</v>
       </c>
       <c r="B82">
-        <v>42</v>
+        <v>53200</v>
       </c>
       <c r="C82">
-        <v>156.18</v>
+        <v>19.11</v>
       </c>
       <c r="D82">
-        <v>78.54000000000001</v>
+        <v>67564</v>
       </c>
       <c r="E82">
-        <v>6559.56</v>
+        <v>1016652</v>
       </c>
       <c r="F82" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G82" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>6559.56</v>
+        <v>1016652</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3135,28 +3120,28 @@
         <v>71</v>
       </c>
       <c r="B83">
-        <v>1926</v>
+        <v>39851</v>
       </c>
       <c r="C83">
-        <v>61.8433</v>
+        <v>75</v>
       </c>
       <c r="D83">
-        <v>-524.64</v>
+        <v>-73724.35000000001</v>
       </c>
       <c r="E83">
-        <v>119110.2</v>
+        <v>2988825</v>
       </c>
       <c r="F83" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G83" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>119110.2</v>
+        <v>2988825</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3164,28 +3149,28 @@
         <v>72</v>
       </c>
       <c r="B84">
-        <v>430000</v>
+        <v>1794</v>
       </c>
       <c r="C84">
-        <v>24.28</v>
+        <v>3</v>
       </c>
       <c r="D84">
-        <v>-180600</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="E84">
-        <v>10440400</v>
+        <v>5382</v>
       </c>
       <c r="F84" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G84" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>10440400</v>
+        <v>5382</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3193,28 +3178,28 @@
         <v>73</v>
       </c>
       <c r="B85">
-        <v>8500</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>363.25</v>
+        <v>1280.34</v>
       </c>
       <c r="D85">
-        <v>19465</v>
+        <v>163.83</v>
       </c>
       <c r="E85">
-        <v>3087625</v>
+        <v>3841.02</v>
       </c>
       <c r="F85" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G85" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>3087625</v>
+        <v>3841.02</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3222,28 +3207,28 @@
         <v>74</v>
       </c>
       <c r="B86">
-        <v>333</v>
+        <v>8000</v>
       </c>
       <c r="C86">
-        <v>0.875</v>
+        <v>1.91</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>291.38</v>
+        <v>15280</v>
       </c>
       <c r="F86" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G86" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H86">
-        <v>0.7822</v>
+        <v>0.7867</v>
       </c>
       <c r="I86">
-        <v>227.92</v>
+        <v>12020.78</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3251,28 +3236,28 @@
         <v>75</v>
       </c>
       <c r="B87">
-        <v>874744</v>
+        <v>787</v>
       </c>
       <c r="C87">
-        <v>29.36</v>
+        <v>582.84</v>
       </c>
       <c r="D87">
-        <v>-78726.96000000001</v>
+        <v>-4958.1</v>
       </c>
       <c r="E87">
-        <v>25682483.84</v>
+        <v>458695.08</v>
       </c>
       <c r="F87" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G87" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
       <c r="I87">
-        <v>25682483.84</v>
+        <v>458695.08</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3280,28 +3265,28 @@
         <v>76</v>
       </c>
       <c r="B88">
-        <v>53200</v>
+        <v>50</v>
       </c>
       <c r="C88">
-        <v>17.84</v>
+        <v>46.48</v>
       </c>
       <c r="D88">
-        <v>-303240</v>
+        <v>38.5</v>
       </c>
       <c r="E88">
-        <v>949088</v>
+        <v>2324</v>
       </c>
       <c r="F88" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G88" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>949088</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3309,28 +3294,28 @@
         <v>77</v>
       </c>
       <c r="B89">
-        <v>39851</v>
+        <v>100</v>
       </c>
       <c r="C89">
-        <v>76.84999999999999</v>
+        <v>62.95</v>
       </c>
       <c r="D89">
-        <v>-21519.54</v>
+        <v>74</v>
       </c>
       <c r="E89">
-        <v>3062549.35</v>
+        <v>6295</v>
       </c>
       <c r="F89" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G89" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>3062549.35</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3338,28 +3323,28 @@
         <v>78</v>
       </c>
       <c r="B90">
-        <v>1794</v>
+        <v>34</v>
       </c>
       <c r="C90">
-        <v>2.96</v>
+        <v>359.76</v>
       </c>
       <c r="D90">
-        <v>-340.86</v>
+        <v>-488.92</v>
       </c>
       <c r="E90">
-        <v>5310.24</v>
+        <v>12231.84</v>
       </c>
       <c r="F90" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G90" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>5310.24</v>
+        <v>12231.84</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3367,28 +3352,28 @@
         <v>79</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>4478</v>
       </c>
       <c r="C91">
-        <v>1225.73</v>
+        <v>28.24</v>
       </c>
       <c r="D91">
-        <v>127.71</v>
+        <v>4433.22</v>
       </c>
       <c r="E91">
-        <v>3677.19</v>
+        <v>126458.72</v>
       </c>
       <c r="F91" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G91" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H91">
         <v>1</v>
       </c>
       <c r="I91">
-        <v>3677.19</v>
+        <v>126458.72</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3396,28 +3381,28 @@
         <v>80</v>
       </c>
       <c r="B92">
-        <v>8000</v>
+        <v>10</v>
       </c>
       <c r="C92">
-        <v>1.91</v>
+        <v>102.3051</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="E92">
-        <v>15280</v>
+        <v>1023.05</v>
       </c>
       <c r="F92" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G92" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H92">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I92">
-        <v>11952.02</v>
+        <v>1023.05</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3425,28 +3410,28 @@
         <v>81</v>
       </c>
       <c r="B93">
-        <v>787</v>
+        <v>45900</v>
       </c>
       <c r="C93">
-        <v>589.14</v>
+        <v>716.08</v>
       </c>
       <c r="D93">
-        <v>14905.78</v>
+        <v>-65637</v>
       </c>
       <c r="E93">
-        <v>463653.18</v>
+        <v>32868072</v>
       </c>
       <c r="F93" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G93" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>463653.18</v>
+        <v>32868072</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3454,28 +3439,28 @@
         <v>82</v>
       </c>
       <c r="B94">
-        <v>50</v>
+        <v>54654</v>
       </c>
       <c r="C94">
-        <v>45.71</v>
+        <v>294.85</v>
       </c>
       <c r="D94">
-        <v>41.5</v>
+        <v>-32792.4</v>
       </c>
       <c r="E94">
-        <v>2285.5</v>
+        <v>16114731.9</v>
       </c>
       <c r="F94" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G94" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94">
-        <v>2285.5</v>
+        <v>16114731.9</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3483,28 +3468,28 @@
         <v>83</v>
       </c>
       <c r="B95">
-        <v>100</v>
+        <v>4320</v>
       </c>
       <c r="C95">
-        <v>62.21</v>
+        <v>220.35</v>
       </c>
       <c r="D95">
-        <v>-19</v>
+        <v>-22204.8</v>
       </c>
       <c r="E95">
-        <v>6221</v>
+        <v>951912</v>
       </c>
       <c r="F95" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G95" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>6221</v>
+        <v>951912</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3512,28 +3497,28 @@
         <v>84</v>
       </c>
       <c r="B96">
-        <v>34</v>
+        <v>82900</v>
       </c>
       <c r="C96">
-        <v>374.14</v>
+        <v>25.16</v>
       </c>
       <c r="D96">
-        <v>-55.08</v>
+        <v>9782.610000000001</v>
       </c>
       <c r="E96">
-        <v>12720.76</v>
+        <v>2085764</v>
       </c>
       <c r="F96" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G96" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I96">
-        <v>12720.76</v>
+        <v>1640870.54</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3541,28 +3526,28 @@
         <v>85</v>
       </c>
       <c r="B97">
-        <v>4478</v>
+        <v>728833</v>
       </c>
       <c r="C97">
-        <v>27.25</v>
+        <v>35.09</v>
       </c>
       <c r="D97">
-        <v>1701.64</v>
+        <v>422723.14</v>
       </c>
       <c r="E97">
-        <v>122025.5</v>
+        <v>25574749.97</v>
       </c>
       <c r="F97" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G97" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H97">
         <v>1</v>
       </c>
       <c r="I97">
-        <v>122025.5</v>
+        <v>25574749.97</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3570,28 +3555,28 @@
         <v>86</v>
       </c>
       <c r="B98">
-        <v>10</v>
+        <v>1085</v>
       </c>
       <c r="C98">
-        <v>101.9368</v>
+        <v>110.88</v>
       </c>
       <c r="D98">
-        <v>-33.83</v>
+        <v>-868</v>
       </c>
       <c r="E98">
-        <v>1019.37</v>
+        <v>120304.8</v>
       </c>
       <c r="F98" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G98" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H98">
         <v>1</v>
       </c>
       <c r="I98">
-        <v>1019.37</v>
+        <v>120304.8</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3599,28 +3584,28 @@
         <v>87</v>
       </c>
       <c r="B99">
-        <v>45900</v>
+        <v>8200</v>
       </c>
       <c r="C99">
-        <v>717.51</v>
+        <v>107.821</v>
       </c>
       <c r="D99">
-        <v>-567324</v>
+        <v>-934.8</v>
       </c>
       <c r="E99">
-        <v>32933709</v>
+        <v>884132.2</v>
       </c>
       <c r="F99" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G99" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H99">
         <v>1</v>
       </c>
       <c r="I99">
-        <v>32933709</v>
+        <v>884132.2</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3628,28 +3613,28 @@
         <v>88</v>
       </c>
       <c r="B100">
-        <v>54654</v>
+        <v>100</v>
       </c>
       <c r="C100">
-        <v>295.45</v>
+        <v>69.2</v>
       </c>
       <c r="D100">
-        <v>-277095.78</v>
+        <v>-62</v>
       </c>
       <c r="E100">
-        <v>16147524.3</v>
+        <v>6920</v>
       </c>
       <c r="F100" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G100" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <v>16147524.3</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3657,28 +3642,28 @@
         <v>89</v>
       </c>
       <c r="B101">
-        <v>4320</v>
+        <v>20100</v>
       </c>
       <c r="C101">
-        <v>225.49</v>
+        <v>2.31</v>
       </c>
       <c r="D101">
-        <v>16632</v>
+        <v>1206</v>
       </c>
       <c r="E101">
-        <v>974116.8</v>
+        <v>46431</v>
       </c>
       <c r="F101" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G101" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H101">
         <v>1</v>
       </c>
       <c r="I101">
-        <v>974116.8</v>
+        <v>46431</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3686,28 +3671,28 @@
         <v>90</v>
       </c>
       <c r="B102">
-        <v>82900</v>
+        <v>18000</v>
       </c>
       <c r="C102">
-        <v>25.01</v>
+        <v>560.92</v>
       </c>
       <c r="D102">
-        <v>-31773.34</v>
+        <v>-159300</v>
       </c>
       <c r="E102">
-        <v>2073329</v>
+        <v>10096560</v>
       </c>
       <c r="F102" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G102" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H102">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I102">
-        <v>1621757.94</v>
+        <v>10096560</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3715,28 +3700,28 @@
         <v>91</v>
       </c>
       <c r="B103">
-        <v>728833</v>
+        <v>-10120</v>
       </c>
       <c r="C103">
-        <v>34.51</v>
+        <v>519.67</v>
       </c>
       <c r="D103">
-        <v>160343.26</v>
+        <v>19901.47</v>
       </c>
       <c r="E103">
-        <v>25152026.83</v>
+        <v>-5259060.4</v>
       </c>
       <c r="F103" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G103" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H103">
         <v>1</v>
       </c>
       <c r="I103">
-        <v>25152026.83</v>
+        <v>-5259060.4</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3744,28 +3729,28 @@
         <v>92</v>
       </c>
       <c r="B104">
-        <v>1085</v>
+        <v>15</v>
       </c>
       <c r="C104">
-        <v>111.68</v>
+        <v>148.35</v>
       </c>
       <c r="D104">
-        <v>1193.5</v>
+        <v>-38.25</v>
       </c>
       <c r="E104">
-        <v>121172.8</v>
+        <v>2225.25</v>
       </c>
       <c r="F104" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G104" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H104">
         <v>1</v>
       </c>
       <c r="I104">
-        <v>121172.8</v>
+        <v>2225.25</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3773,28 +3758,28 @@
         <v>93</v>
       </c>
       <c r="B105">
-        <v>8200</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>107.935</v>
+        <v>290.86</v>
       </c>
       <c r="D105">
-        <v>-17739.88</v>
+        <v>3.98</v>
       </c>
       <c r="E105">
-        <v>885067</v>
+        <v>581.72</v>
       </c>
       <c r="F105" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G105" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H105">
         <v>1</v>
       </c>
       <c r="I105">
-        <v>885067</v>
+        <v>581.72</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3802,28 +3787,28 @@
         <v>94</v>
       </c>
       <c r="B106">
-        <v>100</v>
+        <v>87087</v>
       </c>
       <c r="C106">
-        <v>69.81999999999999</v>
+        <v>72.06</v>
       </c>
       <c r="D106">
-        <v>-15</v>
+        <v>-40930.89</v>
       </c>
       <c r="E106">
-        <v>6982</v>
+        <v>6275489.22</v>
       </c>
       <c r="F106" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G106" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H106">
         <v>1</v>
       </c>
       <c r="I106">
-        <v>6982</v>
+        <v>6275489.22</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3831,28 +3816,28 @@
         <v>95</v>
       </c>
       <c r="B107">
-        <v>20100</v>
+        <v>150200</v>
       </c>
       <c r="C107">
-        <v>2.25</v>
+        <v>40.56</v>
       </c>
       <c r="D107">
-        <v>-804</v>
+        <v>-37811.95</v>
       </c>
       <c r="E107">
-        <v>45225</v>
+        <v>6092112</v>
       </c>
       <c r="F107" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G107" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I107">
-        <v>45225</v>
+        <v>4792664.51</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3860,28 +3845,28 @@
         <v>96</v>
       </c>
       <c r="B108">
-        <v>18000</v>
+        <v>534400</v>
       </c>
       <c r="C108">
-        <v>569.77</v>
+        <v>6.04</v>
       </c>
       <c r="D108">
-        <v>-437400</v>
+        <v>-16816.5</v>
       </c>
       <c r="E108">
-        <v>10255860</v>
+        <v>3227776</v>
       </c>
       <c r="F108" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G108" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H108">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I108">
-        <v>10255860</v>
+        <v>2539291.38</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3889,28 +3874,28 @@
         <v>97</v>
       </c>
       <c r="B109">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>150.9</v>
+        <v>101.29</v>
       </c>
       <c r="D109">
-        <v>-63.9</v>
+        <v>0.77</v>
       </c>
       <c r="E109">
-        <v>2263.5</v>
+        <v>101.29</v>
       </c>
       <c r="F109" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G109" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H109">
         <v>1</v>
       </c>
       <c r="I109">
-        <v>2263.5</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3918,28 +3903,28 @@
         <v>98</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C110">
-        <v>288.87</v>
+        <v>179.06</v>
       </c>
       <c r="D110">
-        <v>-12.24</v>
+        <v>-1.5</v>
       </c>
       <c r="E110">
-        <v>577.74</v>
+        <v>1790.6</v>
       </c>
       <c r="F110" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G110" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H110">
         <v>1</v>
       </c>
       <c r="I110">
-        <v>577.74</v>
+        <v>1790.6</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3947,28 +3932,28 @@
         <v>99</v>
       </c>
       <c r="B111">
-        <v>87087</v>
+        <v>1000</v>
       </c>
       <c r="C111">
-        <v>72.53</v>
+        <v>23.17</v>
       </c>
       <c r="D111">
-        <v>-337026.69</v>
+        <v>-13.4</v>
       </c>
       <c r="E111">
-        <v>6316420.11</v>
+        <v>23170</v>
       </c>
       <c r="F111" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G111" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H111">
         <v>1</v>
       </c>
       <c r="I111">
-        <v>6316420.11</v>
+        <v>23170</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3976,28 +3961,28 @@
         <v>100</v>
       </c>
       <c r="B112">
-        <v>150200</v>
+        <v>168</v>
       </c>
       <c r="C112">
-        <v>40.88</v>
+        <v>706.91</v>
       </c>
       <c r="D112">
-        <v>-29371.23</v>
+        <v>253.68</v>
       </c>
       <c r="E112">
-        <v>6140176</v>
+        <v>118760.88</v>
       </c>
       <c r="F112" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G112" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H112">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I112">
-        <v>4802845.67</v>
+        <v>118760.88</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4005,28 +3990,28 @@
         <v>101</v>
       </c>
       <c r="B113">
-        <v>534400</v>
+        <v>21</v>
       </c>
       <c r="C113">
-        <v>6.08</v>
+        <v>261</v>
       </c>
       <c r="D113">
-        <v>45980.26</v>
+        <v>-242.34</v>
       </c>
       <c r="E113">
-        <v>3249152</v>
+        <v>5481</v>
       </c>
       <c r="F113" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G113" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H113">
-        <v>0.7822</v>
+        <v>1</v>
       </c>
       <c r="I113">
-        <v>2541486.69</v>
+        <v>5481</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4034,28 +4019,28 @@
         <v>102</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C114">
-        <v>100.52</v>
+        <v>142.7</v>
       </c>
       <c r="D114">
-        <v>0.12</v>
+        <v>21.8</v>
       </c>
       <c r="E114">
-        <v>100.52</v>
+        <v>1427</v>
       </c>
       <c r="F114" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G114" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H114">
         <v>1</v>
       </c>
       <c r="I114">
-        <v>100.52</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4063,28 +4048,28 @@
         <v>103</v>
       </c>
       <c r="B115">
-        <v>10</v>
+        <v>739</v>
       </c>
       <c r="C115">
-        <v>179.21</v>
+        <v>160.7</v>
       </c>
       <c r="D115">
-        <v>25.9</v>
+        <v>472.96</v>
       </c>
       <c r="E115">
-        <v>1792.1</v>
+        <v>118757.3</v>
       </c>
       <c r="F115" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G115" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H115">
         <v>1</v>
       </c>
       <c r="I115">
-        <v>1792.1</v>
+        <v>118757.3</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4092,28 +4077,28 @@
         <v>104</v>
       </c>
       <c r="B116">
-        <v>1000</v>
+        <v>1364</v>
       </c>
       <c r="C116">
-        <v>23.1834</v>
+        <v>86.97</v>
       </c>
       <c r="D116">
-        <v>28.4</v>
+        <v>722.92</v>
       </c>
       <c r="E116">
-        <v>23183.4</v>
+        <v>118627.08</v>
       </c>
       <c r="F116" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G116" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H116">
         <v>1</v>
       </c>
       <c r="I116">
-        <v>23183.4</v>
+        <v>118627.08</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4121,28 +4106,28 @@
         <v>105</v>
       </c>
       <c r="B117">
-        <v>168</v>
+        <v>105000</v>
       </c>
       <c r="C117">
-        <v>705.4</v>
+        <v>165.34</v>
       </c>
       <c r="D117">
-        <v>-818.16</v>
+        <v>-22050</v>
       </c>
       <c r="E117">
-        <v>118507.2</v>
+        <v>17360700</v>
       </c>
       <c r="F117" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G117" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H117">
         <v>1</v>
       </c>
       <c r="I117">
-        <v>118507.2</v>
+        <v>17360700</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4150,28 +4135,28 @@
         <v>106</v>
       </c>
       <c r="B118">
-        <v>21</v>
+        <v>6003</v>
       </c>
       <c r="C118">
-        <v>272.54</v>
+        <v>49.36</v>
       </c>
       <c r="D118">
-        <v>-417.69</v>
+        <v>4922.46</v>
       </c>
       <c r="E118">
-        <v>5723.34</v>
+        <v>296308.08</v>
       </c>
       <c r="F118" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G118" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H118">
         <v>1</v>
       </c>
       <c r="I118">
-        <v>5723.34</v>
+        <v>296308.08</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4179,28 +4164,28 @@
         <v>107</v>
       </c>
       <c r="B119">
-        <v>10</v>
+        <v>28600</v>
       </c>
       <c r="C119">
-        <v>140.52</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="D119">
-        <v>-55.9</v>
+        <v>27456</v>
       </c>
       <c r="E119">
-        <v>1405.2</v>
+        <v>2475044</v>
       </c>
       <c r="F119" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G119" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H119">
         <v>1</v>
       </c>
       <c r="I119">
-        <v>1405.2</v>
+        <v>2475044</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4208,28 +4193,28 @@
         <v>108</v>
       </c>
       <c r="B120">
-        <v>739</v>
+        <v>2300</v>
       </c>
       <c r="C120">
-        <v>160.06</v>
+        <v>175.68</v>
       </c>
       <c r="D120">
-        <v>-1308.03</v>
+        <v>13685</v>
       </c>
       <c r="E120">
-        <v>118284.34</v>
+        <v>404064</v>
       </c>
       <c r="F120" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G120" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H120">
         <v>1</v>
       </c>
       <c r="I120">
-        <v>118284.34</v>
+        <v>404064</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4237,28 +4222,28 @@
         <v>109</v>
       </c>
       <c r="B121">
-        <v>1364</v>
+        <v>218100</v>
       </c>
       <c r="C121">
-        <v>86.44</v>
+        <v>4.43</v>
       </c>
       <c r="D121">
-        <v>-1950.52</v>
+        <v>15956.87</v>
       </c>
       <c r="E121">
-        <v>117904.16</v>
+        <v>966183</v>
       </c>
       <c r="F121" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G121" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>0.7867</v>
       </c>
       <c r="I121">
-        <v>117904.16</v>
+        <v>760096.17</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4266,28 +4251,28 @@
         <v>110</v>
       </c>
       <c r="B122">
-        <v>105000</v>
+        <v>458570</v>
       </c>
       <c r="C122">
-        <v>165.55</v>
+        <v>100.59</v>
       </c>
       <c r="D122">
-        <v>-13650</v>
+        <v>9171.4</v>
       </c>
       <c r="E122">
-        <v>17382750</v>
+        <v>46127556.3</v>
       </c>
       <c r="F122" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G122" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H122">
         <v>1</v>
       </c>
       <c r="I122">
-        <v>17382750</v>
+        <v>46127556.3</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -4295,28 +4280,28 @@
         <v>111</v>
       </c>
       <c r="B123">
-        <v>6003</v>
+        <v>270</v>
       </c>
       <c r="C123">
-        <v>48.54</v>
+        <v>42.25</v>
       </c>
       <c r="D123">
-        <v>2881.44</v>
+        <v>18.9</v>
       </c>
       <c r="E123">
-        <v>291385.62</v>
+        <v>11407.5</v>
       </c>
       <c r="F123" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G123" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H123">
         <v>1</v>
       </c>
       <c r="I123">
-        <v>291385.62</v>
+        <v>11407.5</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -4324,173 +4309,28 @@
         <v>112</v>
       </c>
       <c r="B124">
-        <v>28600</v>
+        <v>100</v>
       </c>
       <c r="C124">
-        <v>85.58</v>
+        <v>76.33</v>
       </c>
       <c r="D124">
-        <v>25740</v>
+        <v>39</v>
       </c>
       <c r="E124">
-        <v>2447588</v>
+        <v>7633</v>
       </c>
       <c r="F124" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G124" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
       <c r="I124">
-        <v>2447588</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9">
-      <c r="A125" t="s">
-        <v>113</v>
-      </c>
-      <c r="B125">
-        <v>2300</v>
-      </c>
-      <c r="C125">
-        <v>169.73</v>
-      </c>
-      <c r="D125">
-        <v>6164</v>
-      </c>
-      <c r="E125">
-        <v>390379</v>
-      </c>
-      <c r="F125" t="s">
-        <v>122</v>
-      </c>
-      <c r="G125" t="s">
-        <v>123</v>
-      </c>
-      <c r="H125">
-        <v>1</v>
-      </c>
-      <c r="I125">
-        <v>390379</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9">
-      <c r="A126" t="s">
-        <v>114</v>
-      </c>
-      <c r="B126">
-        <v>218100</v>
-      </c>
-      <c r="C126">
-        <v>4.44</v>
-      </c>
-      <c r="D126">
-        <v>-3411.91</v>
-      </c>
-      <c r="E126">
-        <v>968364</v>
-      </c>
-      <c r="F126" t="s">
-        <v>121</v>
-      </c>
-      <c r="G126" t="s">
-        <v>123</v>
-      </c>
-      <c r="H126">
-        <v>0.7822</v>
-      </c>
-      <c r="I126">
-        <v>757454.3199999999</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9">
-      <c r="A127" t="s">
-        <v>115</v>
-      </c>
-      <c r="B127">
-        <v>458570</v>
-      </c>
-      <c r="C127">
-        <v>100.57</v>
-      </c>
-      <c r="D127">
-        <v>4585.7</v>
-      </c>
-      <c r="E127">
-        <v>46118384.9</v>
-      </c>
-      <c r="F127" t="s">
-        <v>122</v>
-      </c>
-      <c r="G127" t="s">
-        <v>124</v>
-      </c>
-      <c r="H127">
-        <v>1</v>
-      </c>
-      <c r="I127">
-        <v>46118384.9</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
-      <c r="A128" t="s">
-        <v>116</v>
-      </c>
-      <c r="B128">
-        <v>270</v>
-      </c>
-      <c r="C128">
-        <v>42.18</v>
-      </c>
-      <c r="D128">
-        <v>-8.1</v>
-      </c>
-      <c r="E128">
-        <v>11388.6</v>
-      </c>
-      <c r="F128" t="s">
-        <v>122</v>
-      </c>
-      <c r="G128" t="s">
-        <v>124</v>
-      </c>
-      <c r="H128">
-        <v>1</v>
-      </c>
-      <c r="I128">
-        <v>11388.6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9">
-      <c r="A129" t="s">
-        <v>117</v>
-      </c>
-      <c r="B129">
-        <v>100</v>
-      </c>
-      <c r="C129">
-        <v>75.94</v>
-      </c>
-      <c r="D129">
-        <v>-193</v>
-      </c>
-      <c r="E129">
-        <v>7594</v>
-      </c>
-      <c r="F129" t="s">
-        <v>122</v>
-      </c>
-      <c r="G129" t="s">
-        <v>125</v>
-      </c>
-      <c r="H129">
-        <v>1</v>
-      </c>
-      <c r="I129">
-        <v>7594</v>
+        <v>7633</v>
       </c>
     </row>
   </sheetData>
